--- a/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8646C7B4-1DA5-4461-B7A3-5B535B21F97B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FD79F34-F898-4DBC-A5B0-DF86D83EBFB6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC45B6FF-7C50-43E0-91A3-C6E18500D012}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC014858-A876-4C5B-A19B-AC433C1E1075}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B5C095B-59C0-4707-8514-133106441F0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A76DFDE6-3D06-4669-A1B2-645B24BCA5C2}"/>
 </file>